--- a/pcb/v0.3/pico9918_v0_3_bom.xlsx
+++ b/pcb/v0.3/pico9918_v0_3_bom.xlsx
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\troy\OneDrive\Documents\projects\pico9918\pcb\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\troy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4553F85C-1770-4D6D-8FC7-DAE94235AE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CD1522-0E23-47CC-9C6F-431DCCE1B001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2730" windowWidth="38610" windowHeight="18645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -179,9 +192,6 @@
     <t>Resistor Networks &amp; Arrays 1K 5% Convex 4resistors</t>
   </si>
   <si>
-    <t>0804</t>
-  </si>
-  <si>
     <t>Bourns</t>
   </si>
   <si>
@@ -204,6 +214,9 @@
   </si>
   <si>
     <t>PICO9918 v0.3 BOM</t>
+  </si>
+  <si>
+    <t>0402x4</t>
   </si>
 </sst>
 </file>
@@ -323,13 +336,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -699,25 +712,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="19.5" customHeight="1">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="D2" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="D2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="6" spans="1:9" ht="28.5" customHeight="1">
       <c r="A6" s="2" t="s">
@@ -840,13 +853,13 @@
         <v>4</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="G10" s="6">
         <v>603</v>
@@ -867,7 +880,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>25</v>
@@ -876,7 +889,7 @@
         <v>26</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>9</v>
@@ -894,16 +907,16 @@
         <v>3</v>
       </c>
       <c r="D12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>9</v>
